--- a/WWI modell.xlsx
+++ b/WWI modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E708693D-8FC5-E84D-8430-F984BA531DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306FB618-2183-AC43-AD11-F008D75594D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25360" yWindow="500" windowWidth="25520" windowHeight="26500" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -3019,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>665</v>
+        <v>770</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>40</v>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="B6" s="5">
         <f>B4*B5</f>
-        <v>29645.699999999997</v>
+        <v>34326.6</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>42</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="B9" s="6">
         <f>B6-B7+B8</f>
-        <v>29673.269999999997</v>
+        <v>34354.17</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>46</v>
@@ -3893,7 +3893,7 @@
         <v>57</v>
       </c>
       <c r="B11" s="4">
-        <v>9.19</v>
+        <v>9.69</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>48</v>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B13" s="16">
         <f>SOTP!B4</f>
-        <v>0.60506258133967861</v>
+        <v>0.64029415821412805</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>50</v>
@@ -5332,113 +5332,113 @@
       </c>
       <c r="K19" s="21">
         <f t="shared" ref="K19:P19" si="25">(K18/K20)*$B$11</f>
-        <v>16.285554060116645</v>
+        <v>17.171601615074024</v>
       </c>
       <c r="L19" s="21">
         <f t="shared" si="25"/>
-        <v>23.500672947510097</v>
+        <v>24.779273216689099</v>
       </c>
       <c r="M19" s="21">
         <f t="shared" si="25"/>
-        <v>35.45715567519067</v>
+        <v>37.386271870794076</v>
       </c>
       <c r="N19" s="21">
         <f t="shared" si="25"/>
-        <v>28.242036787797218</v>
+        <v>29.778600269179005</v>
       </c>
       <c r="O19" s="21">
         <f t="shared" si="25"/>
-        <v>19.790040376850605</v>
+        <v>20.866756393001346</v>
       </c>
       <c r="P19" s="21">
         <f t="shared" si="25"/>
-        <v>28.242036787797218</v>
+        <v>29.778600269179005</v>
       </c>
       <c r="Q19" s="21">
         <f>(Q18/Q20)*$B$11</f>
-        <v>53.185733512786008</v>
+        <v>56.079407806191121</v>
       </c>
       <c r="R19" s="21">
         <f>(R18/R20)*$B$11</f>
-        <v>30.715791834903545</v>
+        <v>32.386944818304173</v>
       </c>
       <c r="S19" s="21">
         <f>(S18/S20)*$B$11</f>
-        <v>26.592866756393004</v>
+        <v>28.03970390309556</v>
       </c>
       <c r="T19" s="21">
         <f>(T18/T20)*$B$11</f>
-        <v>23.294526693584565</v>
+        <v>24.561911170928667</v>
       </c>
       <c r="U19" s="21"/>
       <c r="V19" s="21"/>
       <c r="Z19" s="18">
         <f t="shared" ref="Z19:AE19" si="26">(Z18*$B$11)/Z20</f>
-        <v>26.799013010318532</v>
+        <v>28.257065948855992</v>
       </c>
       <c r="AA19" s="18">
         <f t="shared" si="26"/>
-        <v>36.694033198743831</v>
+        <v>38.690444145356665</v>
       </c>
       <c r="AB19" s="18">
         <f t="shared" si="26"/>
-        <v>10.92575145805294</v>
+        <v>11.520188425302825</v>
       </c>
       <c r="AC19" s="18">
         <f t="shared" si="26"/>
-        <v>60.194706146253928</v>
+        <v>63.469717362045763</v>
       </c>
       <c r="AD19" s="18">
         <f t="shared" si="26"/>
-        <v>100.80551816958277</v>
+        <v>106.29004037685061</v>
       </c>
       <c r="AE19" s="18">
         <f t="shared" si="26"/>
-        <v>106.57761327949753</v>
+        <v>112.37617765814267</v>
       </c>
       <c r="AF19" s="18">
         <f t="shared" ref="AF19:AP19" si="27">(AF18*$B$11)/AF20</f>
-        <v>138.73642889187977</v>
+        <v>146.28465679676987</v>
       </c>
       <c r="AG19" s="9">
         <f t="shared" si="27"/>
-        <v>128.85223138178554</v>
+        <v>135.86269010767157</v>
       </c>
       <c r="AH19" s="18">
         <f t="shared" si="27"/>
-        <v>124.44536560677426</v>
+        <v>131.21606014468364</v>
       </c>
       <c r="AI19" s="18">
         <f t="shared" si="27"/>
-        <v>120.34027295227675</v>
+        <v>126.88762186154099</v>
       </c>
       <c r="AJ19" s="18">
         <f t="shared" si="27"/>
-        <v>116.52512195553774</v>
+        <v>122.86490008151912</v>
       </c>
       <c r="AK19" s="18">
         <f t="shared" si="27"/>
-        <v>118.45368556072975</v>
+        <v>124.89839097752679</v>
       </c>
       <c r="AL19" s="18">
         <f t="shared" si="27"/>
-        <v>120.43206729739914</v>
+        <v>126.98441045830224</v>
       </c>
       <c r="AM19" s="18">
         <f t="shared" si="27"/>
-        <v>122.46198664667767</v>
+        <v>129.12477155672542</v>
       </c>
       <c r="AN19" s="18">
         <f t="shared" si="27"/>
-        <v>124.54522913650121</v>
+        <v>131.32135694588649</v>
       </c>
       <c r="AO19" s="18">
         <f t="shared" si="27"/>
-        <v>126.68364895615721</v>
+        <v>133.57612169588285</v>
       </c>
       <c r="AP19" s="18">
         <f t="shared" si="27"/>
-        <v>128.87917167514144</v>
+        <v>135.89109614060072</v>
       </c>
     </row>
     <row r="20" spans="3:147" x14ac:dyDescent="0.25">
@@ -5622,27 +5622,27 @@
         <v>0.16600790513833993</v>
       </c>
       <c r="O22" s="25">
-        <f>(O6-K6)/K6</f>
+        <f t="shared" ref="O22:T22" si="31">(O6-K6)/K6</f>
         <v>9.0196078431372548E-2</v>
       </c>
       <c r="P22" s="25">
-        <f>(P6-L6)/L6</f>
+        <f t="shared" si="31"/>
         <v>0.12121212121212122</v>
       </c>
       <c r="Q22" s="25">
-        <f>(Q6-M6)/M6</f>
+        <f t="shared" si="31"/>
         <v>4.3189368770764118E-2</v>
       </c>
       <c r="R22" s="25">
-        <f>(R6-N6)/N6</f>
+        <f t="shared" si="31"/>
         <v>5.0847457627118647E-2</v>
       </c>
       <c r="S22" s="25">
-        <f>(S6-O6)/O6</f>
+        <f t="shared" si="31"/>
         <v>0.11510791366906475</v>
       </c>
       <c r="T22" s="25">
-        <f>(T6-P6)/P6</f>
+        <f t="shared" si="31"/>
         <v>4.0540540540540543E-2</v>
       </c>
       <c r="U22" s="25"/>
@@ -5670,47 +5670,47 @@
         <v>0.10700389105058365</v>
       </c>
       <c r="AF22" s="25">
-        <f t="shared" ref="AF22:AP22" si="31">(AF6-AE6)/AE6</f>
+        <f t="shared" ref="AF22:AP22" si="32">(AF6-AE6)/AE6</f>
         <v>8.0843585237258347E-2</v>
       </c>
       <c r="AG22" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>5.3414634146341497E-2</v>
       </c>
       <c r="AH22" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3.999999999999998E-2</v>
       </c>
       <c r="AI22" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3.9999999999999994E-2</v>
       </c>
       <c r="AJ22" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.0000000000000008E-2</v>
       </c>
       <c r="AK22" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.0000000000000022E-2</v>
       </c>
       <c r="AL22" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.0000000000000098E-2</v>
       </c>
       <c r="AM22" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3.9999999999999987E-2</v>
       </c>
       <c r="AN22" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AO22" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3.999999999999998E-2</v>
       </c>
       <c r="AP22" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.0000000000000049E-2</v>
       </c>
       <c r="AR22" s="32" t="s">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AS22" s="34">
         <f>NPV(AS20,AF18:EQ18)*B11</f>
-        <v>66903.988581980069</v>
+        <v>70544.031486331543</v>
       </c>
     </row>
     <row r="23" spans="3:147" x14ac:dyDescent="0.25">
@@ -5742,55 +5742,55 @@
         <v>2.4390243902439025E-2</v>
       </c>
       <c r="H23" s="22">
-        <f t="shared" ref="H23:N23" si="32">H11/H6</f>
+        <f t="shared" ref="H23:N23" si="33">H11/H6</f>
         <v>9.5785440613026823E-2</v>
       </c>
       <c r="I23" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>9.6525096525096526E-2</v>
       </c>
       <c r="J23" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.3003952569169967E-2</v>
       </c>
       <c r="K23" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>6.2745098039215685E-2</v>
       </c>
       <c r="L23" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="M23" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>9.9667774086378738E-2</v>
       </c>
       <c r="N23" s="22">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.4576271186440682E-2</v>
       </c>
       <c r="O23" s="22">
-        <f>O11/O6</f>
+        <f t="shared" ref="O23:T23" si="34">O11/O6</f>
         <v>3.9568345323741004E-2</v>
       </c>
       <c r="P23" s="22">
-        <f>P11/P6</f>
+        <f t="shared" si="34"/>
         <v>0.10472972972972973</v>
       </c>
       <c r="Q23" s="22">
-        <f>Q11/Q6</f>
+        <f t="shared" si="34"/>
         <v>8.9171974522292988E-2</v>
       </c>
       <c r="R23" s="22">
-        <f>R11/R6</f>
+        <f t="shared" si="34"/>
         <v>6.4516129032258063E-2</v>
       </c>
       <c r="S23" s="22">
-        <f>S11/S6</f>
+        <f t="shared" si="34"/>
         <v>8.7096774193548387E-2</v>
       </c>
       <c r="T23" s="22">
-        <f>T11/T6</f>
+        <f t="shared" si="34"/>
         <v>0.10714285714285714</v>
       </c>
       <c r="U23" s="22"/>
@@ -5798,71 +5798,71 @@
       <c r="W23" s="22"/>
       <c r="X23" s="22"/>
       <c r="Z23" s="22">
-        <f t="shared" ref="Z23:AE23" si="33">Z11/Z6</f>
+        <f t="shared" ref="Z23:AE23" si="35">Z11/Z6</f>
         <v>9.1764705882352943E-2</v>
       </c>
       <c r="AA23" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>7.5123152709359611E-2</v>
       </c>
       <c r="AB23" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>8.3428571428571435E-2</v>
       </c>
       <c r="AC23" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>8.7682672233820466E-2</v>
       </c>
       <c r="AD23" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>8.6575875486381321E-2</v>
       </c>
       <c r="AE23" s="22">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>7.3813708260105443E-2</v>
       </c>
       <c r="AF23" s="22">
-        <f t="shared" ref="AF23:AP23" si="34">AF11/AF6</f>
+        <f t="shared" ref="AF23:AP23" si="36">AF11/AF6</f>
         <v>8.6178861788617889E-2</v>
       </c>
       <c r="AG23" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.9141004862236639E-2</v>
       </c>
       <c r="AH23" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.91410048622365E-2</v>
       </c>
       <c r="AI23" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.9141004862236597E-2</v>
       </c>
       <c r="AJ23" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.914100486223657E-2</v>
       </c>
       <c r="AK23" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.9141004862236584E-2</v>
       </c>
       <c r="AL23" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.9141004862236667E-2</v>
       </c>
       <c r="AM23" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.9141004862236653E-2</v>
       </c>
       <c r="AN23" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.9141004862236639E-2</v>
       </c>
       <c r="AO23" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.9141004862236695E-2</v>
       </c>
       <c r="AP23" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.9141004862236639E-2</v>
       </c>
       <c r="AR23" s="2" t="s">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="AS24" s="35">
         <f>AS22/AS23</f>
-        <v>1500.7624177205041</v>
+        <v>1582.4143446911519</v>
       </c>
     </row>
     <row r="25" spans="3:147" x14ac:dyDescent="0.25">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AS25" s="37">
         <f>(AS24-B4)/B4</f>
-        <v>1.256785590557149</v>
+        <v>1.0550835645339636</v>
       </c>
     </row>
     <row r="26" spans="3:147" x14ac:dyDescent="0.25">
@@ -6706,67 +6706,67 @@
         <v>97</v>
       </c>
       <c r="D37" s="17">
-        <f t="shared" ref="D37:T37" si="35">SUM(D26:D36)</f>
+        <f t="shared" ref="D37:S37" si="37">SUM(D26:D36)</f>
         <v>3701</v>
       </c>
       <c r="E37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3392</v>
       </c>
       <c r="F37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3271</v>
       </c>
       <c r="G37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3628</v>
       </c>
       <c r="H37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3795</v>
       </c>
       <c r="I37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3556</v>
       </c>
       <c r="J37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3641</v>
       </c>
       <c r="K37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3735</v>
       </c>
       <c r="L37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4113</v>
       </c>
       <c r="M37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3814</v>
       </c>
       <c r="N37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3967</v>
       </c>
       <c r="O37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3758</v>
       </c>
       <c r="P37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4022</v>
       </c>
       <c r="Q37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4294</v>
       </c>
       <c r="R37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4443</v>
       </c>
       <c r="S37" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4411</v>
       </c>
       <c r="T37" s="17">
@@ -7077,67 +7077,67 @@
         <v>102</v>
       </c>
       <c r="D42" s="15">
-        <f t="shared" ref="D42:T42" si="36">SUM(D38:D41)</f>
+        <f t="shared" ref="D42:S42" si="38">SUM(D38:D41)</f>
         <v>2394</v>
       </c>
       <c r="E42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2187</v>
       </c>
       <c r="F42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2093</v>
       </c>
       <c r="G42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2356</v>
       </c>
       <c r="H42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2495</v>
       </c>
       <c r="I42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2347</v>
       </c>
       <c r="J42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2457</v>
       </c>
       <c r="K42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2487</v>
       </c>
       <c r="L42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2890</v>
       </c>
       <c r="M42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2654</v>
       </c>
       <c r="N42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2807</v>
       </c>
       <c r="O42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2695</v>
       </c>
       <c r="P42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2891</v>
       </c>
       <c r="Q42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3190</v>
       </c>
       <c r="R42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3335</v>
       </c>
       <c r="S42" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3275</v>
       </c>
       <c r="T42" s="15">
@@ -7874,55 +7874,55 @@
         <v>111</v>
       </c>
       <c r="D53" s="15">
-        <f t="shared" ref="D53:P53" si="37">SUM(D43:D52)</f>
+        <f t="shared" ref="D53:P53" si="39">SUM(D43:D52)</f>
         <v>1309</v>
       </c>
       <c r="E53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1206</v>
       </c>
       <c r="F53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1179</v>
       </c>
       <c r="G53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1273</v>
       </c>
       <c r="H53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1299</v>
       </c>
       <c r="I53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1210</v>
       </c>
       <c r="J53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1185</v>
       </c>
       <c r="K53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1249</v>
       </c>
       <c r="L53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1224</v>
       </c>
       <c r="M53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1161</v>
       </c>
       <c r="N53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1162</v>
       </c>
       <c r="O53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1063</v>
       </c>
       <c r="P53" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1131</v>
       </c>
       <c r="Q53" s="15">
@@ -7961,55 +7961,55 @@
         <v>112</v>
       </c>
       <c r="D54" s="17">
-        <f t="shared" ref="D54:P54" si="38">D42+D53</f>
+        <f t="shared" ref="D54:P54" si="40">D42+D53</f>
         <v>3703</v>
       </c>
       <c r="E54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3393</v>
       </c>
       <c r="F54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3272</v>
       </c>
       <c r="G54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3629</v>
       </c>
       <c r="H54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3794</v>
       </c>
       <c r="I54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3557</v>
       </c>
       <c r="J54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3642</v>
       </c>
       <c r="K54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3736</v>
       </c>
       <c r="L54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>4114</v>
       </c>
       <c r="M54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3815</v>
       </c>
       <c r="N54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3969</v>
       </c>
       <c r="O54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3758</v>
       </c>
       <c r="P54" s="17">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>4022</v>
       </c>
       <c r="Q54" s="17">
@@ -8078,71 +8078,71 @@
         <v>58</v>
       </c>
       <c r="D57" s="13">
-        <f t="shared" ref="D57:N57" si="39">D16</f>
+        <f t="shared" ref="D57:N57" si="41">D16</f>
         <v>165</v>
       </c>
       <c r="E57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-45</v>
       </c>
       <c r="F57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-24</v>
       </c>
       <c r="G57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>211</v>
       </c>
       <c r="H57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>107</v>
       </c>
       <c r="I57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>164</v>
       </c>
       <c r="J57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>157</v>
       </c>
       <c r="K57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>90</v>
       </c>
       <c r="L57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>116</v>
       </c>
       <c r="M57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>179</v>
       </c>
       <c r="N57" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>144</v>
       </c>
       <c r="O57" s="13">
-        <f>O16</f>
+        <f t="shared" ref="O57:T57" si="42">O16</f>
         <v>100</v>
       </c>
       <c r="P57" s="13">
-        <f>P16</f>
+        <f t="shared" si="42"/>
         <v>149</v>
       </c>
       <c r="Q57" s="13">
-        <f>Q16</f>
+        <f t="shared" si="42"/>
         <v>266</v>
       </c>
       <c r="R57" s="13">
-        <f>R16</f>
+        <f t="shared" si="42"/>
         <v>152</v>
       </c>
       <c r="S57" s="13">
-        <f>S16</f>
+        <f t="shared" si="42"/>
         <v>154</v>
       </c>
       <c r="T57" s="13">
-        <f>T16</f>
+        <f t="shared" si="42"/>
         <v>120</v>
       </c>
       <c r="U57" s="13"/>
@@ -8151,31 +8151,31 @@
       <c r="X57" s="13"/>
       <c r="Y57" s="13"/>
       <c r="Z57" s="13">
-        <f t="shared" ref="Z57:AF57" si="40">Z16</f>
+        <f t="shared" ref="Z57:AF57" si="43">Z16</f>
         <v>145</v>
       </c>
       <c r="AA57" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>205</v>
       </c>
       <c r="AB57" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>66</v>
       </c>
       <c r="AC57" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>305</v>
       </c>
       <c r="AD57" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>516</v>
       </c>
       <c r="AE57" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>537</v>
       </c>
       <c r="AF57" s="13">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>721</v>
       </c>
     </row>
@@ -8837,47 +8837,47 @@
         <v>31</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" ref="D66:N66" si="41">SUM(D58:D65)</f>
+        <f t="shared" ref="D66:N66" si="44">SUM(D58:D65)</f>
         <v>3</v>
       </c>
       <c r="E66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6</v>
       </c>
       <c r="F66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>28</v>
       </c>
       <c r="G66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>28</v>
       </c>
       <c r="H66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>42</v>
       </c>
       <c r="I66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>18</v>
       </c>
       <c r="J66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>70</v>
       </c>
       <c r="K66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>64</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>34</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>14</v>
       </c>
       <c r="N66" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>44</v>
       </c>
       <c r="O66" s="1">
@@ -8909,31 +8909,31 @@
       <c r="X66" s="13"/>
       <c r="Y66" s="1"/>
       <c r="Z66" s="1">
-        <f t="shared" ref="Z66:AF66" si="42">SUM(Z58:Z65)</f>
+        <f t="shared" ref="Z66:AF66" si="45">SUM(Z58:Z65)</f>
         <v>99</v>
       </c>
       <c r="AA66" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>196</v>
       </c>
       <c r="AB66" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>121</v>
       </c>
       <c r="AC66" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>64</v>
       </c>
       <c r="AD66" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>194</v>
       </c>
       <c r="AE66" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>96</v>
       </c>
       <c r="AF66" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>219</v>
       </c>
     </row>
@@ -9812,71 +9812,71 @@
         <v>33</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" ref="D79:N79" si="43">SUM(D68:D78)</f>
+        <f t="shared" ref="D79:N79" si="46">SUM(D68:D78)</f>
         <v>-43</v>
       </c>
       <c r="E79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>56</v>
       </c>
       <c r="F79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>-13</v>
       </c>
       <c r="G79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>6</v>
       </c>
       <c r="H79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>-50</v>
       </c>
       <c r="I79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>95</v>
       </c>
       <c r="J79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>-13</v>
       </c>
       <c r="K79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>-31</v>
       </c>
       <c r="M79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>96</v>
       </c>
       <c r="N79" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>-21</v>
       </c>
       <c r="O79" s="1">
-        <f>SUM(O68:O78)</f>
+        <f t="shared" ref="O79:T79" si="47">SUM(O68:O78)</f>
         <v>175</v>
       </c>
       <c r="P79" s="1">
-        <f>SUM(P68:P78)</f>
+        <f t="shared" si="47"/>
         <v>-27</v>
       </c>
       <c r="Q79" s="1">
-        <f>SUM(Q68:Q78)</f>
+        <f t="shared" si="47"/>
         <v>98</v>
       </c>
       <c r="R79" s="1">
-        <f>SUM(R68:R78)</f>
+        <f t="shared" si="47"/>
         <v>76</v>
       </c>
       <c r="S79" s="1">
-        <f>SUM(S68:S78)</f>
+        <f t="shared" si="47"/>
         <v>17</v>
       </c>
       <c r="T79" s="1">
-        <f>SUM(T68:T78)</f>
+        <f t="shared" si="47"/>
         <v>92</v>
       </c>
       <c r="U79" s="1"/>
@@ -9885,31 +9885,31 @@
       <c r="X79" s="13"/>
       <c r="Y79" s="1"/>
       <c r="Z79" s="1">
-        <f t="shared" ref="Z79:AF79" si="44">SUM(Z68:Z78)</f>
+        <f t="shared" ref="Z79:AF79" si="48">SUM(Z68:Z78)</f>
         <v>81</v>
       </c>
       <c r="AA79" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>42</v>
       </c>
       <c r="AB79" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>-53</v>
       </c>
       <c r="AC79" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>6</v>
       </c>
       <c r="AD79" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>64</v>
       </c>
       <c r="AE79" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>216</v>
       </c>
       <c r="AF79" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>164</v>
       </c>
     </row>
@@ -10548,11 +10548,11 @@
         <v>32</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" ref="D89:N89" si="45">SUM(D81:D88)</f>
+        <f t="shared" ref="D89:N89" si="49">SUM(D81:D88)</f>
         <v>-7</v>
       </c>
       <c r="E89" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>-83</v>
       </c>
       <c r="F89" s="1">
@@ -10560,59 +10560,59 @@
         <v>-21</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>-29</v>
       </c>
       <c r="H89" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>-41</v>
       </c>
       <c r="I89" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>-97</v>
       </c>
       <c r="J89" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>-49</v>
       </c>
       <c r="K89" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>-57</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>-41</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>-119</v>
       </c>
       <c r="N89" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>-47</v>
       </c>
       <c r="O89" s="1">
-        <f>SUM(O81:O88)</f>
+        <f t="shared" ref="O89:T89" si="50">SUM(O81:O88)</f>
         <v>-175</v>
       </c>
       <c r="P89" s="1">
-        <f>SUM(P81:P88)</f>
+        <f t="shared" si="50"/>
         <v>-7</v>
       </c>
       <c r="Q89" s="1">
-        <f>SUM(Q81:Q88)</f>
+        <f t="shared" si="50"/>
         <v>-118</v>
       </c>
       <c r="R89" s="1">
-        <f>SUM(R81:R88)</f>
+        <f t="shared" si="50"/>
         <v>-34</v>
       </c>
       <c r="S89" s="1">
-        <f>SUM(S81:S88)</f>
+        <f t="shared" si="50"/>
         <v>-185</v>
       </c>
       <c r="T89" s="1">
-        <f>SUM(T81:T88)</f>
+        <f t="shared" si="50"/>
         <v>-23</v>
       </c>
       <c r="U89" s="1"/>
@@ -10621,31 +10621,31 @@
       <c r="X89" s="13"/>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1">
-        <f t="shared" ref="Z89:AF89" si="46">SUM(Z81:Z88)</f>
+        <f t="shared" ref="Z89:AF89" si="51">SUM(Z81:Z88)</f>
         <v>-165</v>
       </c>
       <c r="AA89" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>-120</v>
       </c>
       <c r="AB89" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>-106</v>
       </c>
       <c r="AC89" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>-140</v>
       </c>
       <c r="AD89" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>-197</v>
       </c>
       <c r="AE89" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>-381</v>
       </c>
       <c r="AF89" s="1">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>-344</v>
       </c>
     </row>
@@ -10658,101 +10658,101 @@
         <v>83</v>
       </c>
       <c r="D91" s="2">
-        <f t="shared" ref="D91:N91" si="47">D66+D79+D89</f>
+        <f t="shared" ref="D91:N91" si="52">D66+D79+D89</f>
         <v>-47</v>
       </c>
       <c r="E91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>-21</v>
       </c>
       <c r="F91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>-6</v>
       </c>
       <c r="G91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>5</v>
       </c>
       <c r="H91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>-49</v>
       </c>
       <c r="I91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>16</v>
       </c>
       <c r="J91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>8</v>
       </c>
       <c r="K91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>38</v>
       </c>
       <c r="L91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>-38</v>
       </c>
       <c r="M91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>-9</v>
       </c>
       <c r="N91" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>-24</v>
       </c>
       <c r="O91" s="2">
-        <f>O66+O79+O89</f>
+        <f t="shared" ref="O91:T91" si="53">O66+O79+O89</f>
         <v>2</v>
       </c>
       <c r="P91" s="2">
-        <f>P66+P79+P89</f>
+        <f t="shared" si="53"/>
         <v>3</v>
       </c>
       <c r="Q91" s="2">
-        <f>Q66+Q79+Q89</f>
+        <f t="shared" si="53"/>
         <v>22</v>
       </c>
       <c r="R91" s="2">
-        <f>R66+R79+R89</f>
+        <f t="shared" si="53"/>
         <v>96</v>
       </c>
       <c r="S91" s="2">
-        <f>S66+S79+S89</f>
+        <f t="shared" si="53"/>
         <v>-82</v>
       </c>
       <c r="T91" s="2">
-        <f>T66+T79+T89</f>
+        <f t="shared" si="53"/>
         <v>64</v>
       </c>
       <c r="W91" s="13"/>
       <c r="X91" s="13"/>
       <c r="Z91" s="2">
-        <f t="shared" ref="Z91:AF91" si="48">Z66+Z79+Z89</f>
+        <f t="shared" ref="Z91:AF91" si="54">Z66+Z79+Z89</f>
         <v>15</v>
       </c>
       <c r="AA91" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>118</v>
       </c>
       <c r="AB91" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>-38</v>
       </c>
       <c r="AC91" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>-70</v>
       </c>
       <c r="AD91" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>61</v>
       </c>
       <c r="AE91" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>-69</v>
       </c>
       <c r="AF91" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>39</v>
       </c>
     </row>
@@ -10765,19 +10765,19 @@
         <v>84</v>
       </c>
       <c r="D93" s="2">
-        <f t="shared" ref="D93:N93" si="49">D66+D68+D70+D72</f>
+        <f t="shared" ref="D93:N93" si="55">D66+D68+D70+D72</f>
         <v>-5</v>
       </c>
       <c r="E93" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>24</v>
       </c>
       <c r="F93" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>13</v>
       </c>
       <c r="G93" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>11</v>
       </c>
       <c r="H93" s="2">
@@ -10789,77 +10789,77 @@
         <v>96</v>
       </c>
       <c r="J93" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>58</v>
       </c>
       <c r="K93" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>108</v>
       </c>
       <c r="L93" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>3</v>
       </c>
       <c r="M93" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>106</v>
       </c>
       <c r="N93" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>38</v>
       </c>
       <c r="O93" s="2">
-        <f>O66+O68+O70+O72</f>
+        <f t="shared" ref="O93:T93" si="56">O66+O68+O70+O72</f>
         <v>165</v>
       </c>
       <c r="P93" s="2">
-        <f>P66+P68+P70+P72</f>
+        <f t="shared" si="56"/>
         <v>14</v>
       </c>
       <c r="Q93" s="2">
-        <f>Q66+Q68+Q70+Q72</f>
+        <f t="shared" si="56"/>
         <v>226</v>
       </c>
       <c r="R93" s="2">
-        <f>R66+R68+R70+R72</f>
+        <f t="shared" si="56"/>
         <v>216</v>
       </c>
       <c r="S93" s="2">
-        <f>S66+S68+S70+S72</f>
+        <f t="shared" si="56"/>
         <v>46</v>
       </c>
       <c r="T93" s="2">
-        <f>T66+T68+T70+T72</f>
+        <f t="shared" si="56"/>
         <v>139</v>
       </c>
       <c r="W93" s="13"/>
       <c r="X93" s="13"/>
       <c r="Z93" s="2">
-        <f t="shared" ref="Z93:AF93" si="50">Z66+Z68+Z70+Z72</f>
+        <f t="shared" ref="Z93:AF93" si="57">Z66+Z68+Z70+Z72</f>
         <v>126</v>
       </c>
       <c r="AA93" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="57"/>
         <v>180</v>
       </c>
       <c r="AB93" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="57"/>
         <v>53</v>
       </c>
       <c r="AC93" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="57"/>
         <v>34</v>
       </c>
       <c r="AD93" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="57"/>
         <v>271</v>
       </c>
       <c r="AE93" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="57"/>
         <v>312</v>
       </c>
       <c r="AF93" s="2">
-        <f t="shared" si="50"/>
+        <f t="shared" si="57"/>
         <v>502</v>
       </c>
     </row>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="B4" s="65">
         <f>Modell!B4/SOTP!G27</f>
-        <v>0.60506258133967861</v>
+        <v>0.64029415821412805</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -14792,15 +14792,15 @@
       </c>
       <c r="E8" s="64">
         <f>B30</f>
-        <v>9.19</v>
+        <v>9.69</v>
       </c>
       <c r="F8" s="68">
         <f>(B8*E8)*D8</f>
-        <v>11487500000</v>
+        <v>12112500000</v>
       </c>
       <c r="G8" s="69">
         <f>F8/$B$27</f>
-        <v>257.68281740690895</v>
+        <v>271.70255720053837</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
@@ -14815,15 +14815,15 @@
       </c>
       <c r="E9" s="64">
         <f>B30</f>
-        <v>9.19</v>
+        <v>9.69</v>
       </c>
       <c r="F9" s="68">
         <f>(B9*E9)*D9</f>
-        <v>6616800000</v>
+        <v>6976800000</v>
       </c>
       <c r="G9" s="69">
         <f>F9/$B$27</f>
-        <v>148.42530282637955</v>
+        <v>156.50067294751008</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
@@ -14839,15 +14839,15 @@
       </c>
       <c r="E10" s="70">
         <f>B30</f>
-        <v>9.19</v>
+        <v>9.69</v>
       </c>
       <c r="F10" s="71">
         <f>(B10*E10)*D10</f>
-        <v>-551400000</v>
+        <v>-581400000</v>
       </c>
       <c r="G10" s="72">
         <f>F10/$B$27</f>
-        <v>-12.368775235531629</v>
+        <v>-13.041722745625842</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
@@ -14861,7 +14861,7 @@
       <c r="F11" s="66"/>
       <c r="G11" s="73">
         <f>SUM(G8:G10)</f>
-        <v>393.73934499775686</v>
+        <v>415.16150740242256</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
@@ -14898,18 +14898,18 @@
         <v>160210000</v>
       </c>
       <c r="D14" s="64">
-        <v>115</v>
+        <v>144.4</v>
       </c>
       <c r="E14" s="64">
         <v>1</v>
       </c>
       <c r="F14" s="68">
         <f>B14*D14</f>
-        <v>18424150000</v>
+        <v>23134324000</v>
       </c>
       <c r="G14" s="69">
         <f>F14/$B$27</f>
-        <v>413.28286227007629</v>
+        <v>518.93952445042623</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
@@ -14920,19 +14920,19 @@
         <v>8250000</v>
       </c>
       <c r="D15" s="68">
-        <v>225500</v>
+        <v>195000</v>
       </c>
       <c r="E15" s="64">
         <f>B31</f>
-        <v>6.1999999999999998E-3</v>
+        <v>6.6E-3</v>
       </c>
       <c r="F15" s="68">
         <f>(B15*D15)*E15</f>
-        <v>11534325000</v>
+        <v>10617750000</v>
       </c>
       <c r="G15" s="69">
         <f>F15/$B$27</f>
-        <v>258.73317631224762</v>
+        <v>238.17294751009422</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
@@ -14943,18 +14943,18 @@
         <v>96844009</v>
       </c>
       <c r="D16" s="64">
-        <v>6.45</v>
+        <v>4.95</v>
       </c>
       <c r="E16" s="64">
         <v>1</v>
       </c>
       <c r="F16" s="68">
         <f>(B16*D16)</f>
-        <v>624643858.05000007</v>
+        <v>479377844.55000001</v>
       </c>
       <c r="G16" s="69">
         <f>F16/$B$27</f>
-        <v>14.011750965679678</v>
+        <v>10.7532042294751</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
@@ -14970,15 +14970,15 @@
       </c>
       <c r="E17" s="70">
         <f>B32</f>
-        <v>6.66</v>
+        <v>6.75</v>
       </c>
       <c r="F17" s="71">
         <f>(B17*D17)*E17</f>
-        <v>832500000</v>
+        <v>843750000</v>
       </c>
       <c r="G17" s="72">
         <f>F17/$B$27</f>
-        <v>18.674293405114401</v>
+        <v>18.926648721399729</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
@@ -14992,7 +14992,7 @@
       <c r="F18" s="66"/>
       <c r="G18" s="73">
         <f>SUM(G14:G17)</f>
-        <v>704.70208295311807</v>
+        <v>786.79232491139521</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
@@ -15068,11 +15068,11 @@
       </c>
       <c r="F27" s="68">
         <f>SUM(F8:F10)+SUM(F14:F17)-F21+F24</f>
-        <v>48996088858.050003</v>
+        <v>53610671844.550003</v>
       </c>
       <c r="G27" s="82">
         <f>F27/B27</f>
-        <v>1099.0598667126515</v>
+        <v>1202.5722710755945</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
@@ -15090,7 +15090,7 @@
         <v>57</v>
       </c>
       <c r="B30" s="80">
-        <v>9.19</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
@@ -15098,7 +15098,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="80">
-        <v>6.1999999999999998E-3</v>
+        <v>6.6E-3</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
@@ -15106,7 +15106,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="80">
-        <v>6.66</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="B92" s="69">
         <f>G8</f>
-        <v>257.68281740690895</v>
+        <v>271.70255720053837</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="B93" s="69">
         <f>G9</f>
-        <v>148.42530282637955</v>
+        <v>156.50067294751008</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="B94" s="72">
         <f>G10</f>
-        <v>-12.368775235531629</v>
+        <v>-13.041722745625842</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="B95" s="73">
         <f>SUM(B92:B94)</f>
-        <v>393.73934499775686</v>
+        <v>415.16150740242256</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="B97" s="69">
         <f>G14</f>
-        <v>413.28286227007629</v>
+        <v>518.93952445042623</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.4">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="B98" s="69">
         <f>G15</f>
-        <v>258.73317631224762</v>
+        <v>238.17294751009422</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="B99" s="69">
         <f>G16</f>
-        <v>14.011750965679678</v>
+        <v>10.7532042294751</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="B100" s="72">
         <f>G17</f>
-        <v>18.674293405114401</v>
+        <v>18.926648721399729</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="B101" s="73">
         <f>SUM(B97:B100)</f>
-        <v>704.70208295311807</v>
+        <v>786.79232491139521</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="B106" s="69">
         <f>B95+B101+B103+B104</f>
-        <v>1099.0598667126515</v>
+        <v>1202.5722710755942</v>
       </c>
     </row>
   </sheetData>
@@ -15251,15 +15251,15 @@
       </c>
       <c r="D5" s="36">
         <f>Modell!$B$9/(Modell!AF11*Modell!$B$11)</f>
-        <v>30.460991233292955</v>
+        <v>33.446433787020275</v>
       </c>
       <c r="E5" s="36">
         <f>Modell!$B$9/(Modell!AG11*Modell!$B$11)</f>
-        <v>27.955541737913876</v>
+        <v>30.695428410598684</v>
       </c>
       <c r="F5" s="36">
         <f>Modell!$B$9/(Modell!AH11*Modell!$B$11)</f>
-        <v>26.880328594148004</v>
+        <v>29.514835010191092</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -15268,15 +15268,15 @@
       </c>
       <c r="D6" s="36">
         <f>Modell!$B$4/Modell!AF19</f>
-        <v>4.7932616206969589</v>
+        <v>5.2637099259818099</v>
       </c>
       <c r="E6" s="36">
         <f>Modell!$B$4/Modell!AG19</f>
-        <v>5.1609505933166471</v>
+        <v>5.6674867794077448</v>
       </c>
       <c r="F6" s="36">
         <f>Modell!$B$4/Modell!AH19</f>
-        <v>5.34371044480101</v>
+        <v>5.8681841167229818</v>
       </c>
     </row>
   </sheetData>
